--- a/PCDN域名URL关键字.xlsx
+++ b/PCDN域名URL关键字.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30514"/>
+  <fileSharing readOnlyRecommended="1"/>
   <workbookPr autoCompressPictures="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面\QQ文件\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\下载\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:201_{F20F2D82-DBBA-4613-8724-3BC593B44B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="9qAF2+DtxfJH00hI65oRU+eMwY9KzfEARK+RHZzYeRKsLpMPantgfdAEv0/85JmJ2vchcWrG/gL+Xm43OQEJeg==" workbookSaltValue="Y+x1Z4pLCr1D/IOjMMMUEg==" workbookSpinCount="100000" lockStructure="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C43CE32-5C41-43A0-81F2-FCBD273623E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="DXb0YbIsVpSGgkX6q1PJKkLMMRGxsFDXRlb0DCBPsFvwmTyN5UTFS16RSJQ9iWcTSXy1FkflSgFYqYUtyZX+Pw==" workbookSaltValue="eHN5bAVOIjbxTQC04KItdw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" activeTab="2" xr2:uid="{635FD1CB-08EF-4A62-AA24-FB7602255245}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" activeTab="1" xr2:uid="{635FD1CB-08EF-4A62-AA24-FB7602255245}"/>
   </bookViews>
   <sheets>
     <sheet name="IP ACL（高级）" sheetId="2" r:id="rId1"/>
-    <sheet name="更新说明" sheetId="8" r:id="rId2"/>
+    <sheet name="更新说明" sheetId="9" r:id="rId2"/>
     <sheet name="PCDN域名" sheetId="1" r:id="rId3"/>
     <sheet name="Hosts" sheetId="3" r:id="rId4"/>
     <sheet name="海外" sheetId="4" r:id="rId5"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="651">
   <si>
     <t>序号</t>
   </si>
@@ -2126,19 +2127,167 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>v. 4.2.3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026.05.30 13时</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>第19次修订（阶段性主要版本）</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Vivo商店，慎用！</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>260916新增</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>这些貌似有奇效，但是未经广泛测试和验证</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>可根据实际情况，先开一些并快速回退</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>总之知道这些是测试项目，删的时候也有范围就好</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>域名</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>A1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>A2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>kwai</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>xyydedge</t>
+  </si>
+  <si>
+    <t>oppass</t>
+  </si>
+  <si>
+    <t>willcdn</t>
+  </si>
+  <si>
+    <t>ksapisrv</t>
+  </si>
+  <si>
+    <t>kwimgs</t>
+  </si>
+  <si>
+    <t>hongboluo</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
+    <t>A8</t>
+  </si>
+  <si>
+    <t>A9</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>A11</t>
+  </si>
+  <si>
+    <t>A12</t>
+  </si>
+  <si>
+    <t>qjsalia</t>
+  </si>
+  <si>
+    <t>ndcimgs</t>
+  </si>
+  <si>
+    <t>xyydnode</t>
+  </si>
+  <si>
+    <t>smtcdns</t>
+  </si>
+  <si>
+    <t>! ---------- [7.网友的最新补充] ----------</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>||*.kwaicdn.*</t>
+  </si>
+  <si>
+    <t>||cdndns.kwd.inkuai.com</t>
+  </si>
+  <si>
+    <t>||*.ecukwai.com</t>
+  </si>
+  <si>
+    <t>||p5*.*kwai.com</t>
+  </si>
+  <si>
+    <t>||p2p*.xxpkg.com</t>
+  </si>
+  <si>
+    <t>||*.xyydedge.*</t>
+  </si>
+  <si>
+    <t>||*.oppass.*</t>
+  </si>
+  <si>
+    <t>||*.wxlivecdn.*</t>
+  </si>
+  <si>
+    <t>||*.willcdn.*</t>
+  </si>
+  <si>
+    <t>||*.xxpkg.*</t>
+  </si>
+  <si>
+    <t>||*.ksapisrv.*</t>
+  </si>
+  <si>
+    <t>||*.kwimgs.*</t>
+  </si>
+  <si>
+    <t>||*.hongboluo.*</t>
+  </si>
+  <si>
+    <t>||*.qjsalia.*</t>
+  </si>
+  <si>
+    <t>||*.ndcimgs.*</t>
+  </si>
+  <si>
+    <t>||*.xyydnode.*</t>
+  </si>
+  <si>
+    <t>||*.smtcdns.* !抖音pcdn</t>
+  </si>
+  <si>
+    <t>第20次修订（阶段性主要版本）</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 4.4</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.09.16 23时</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3443,6 +3592,9 @@
     <xf numFmtId="0" fontId="47" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3472,9 +3624,6 @@
     </xf>
     <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -3692,7 +3841,7 @@
         <xdr:cNvPr id="2" name="图片 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DFF7664-0F96-46EC-993A-26828C4585E6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B77E363-C6F6-4022-98CB-0C2D3A39F622}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3715,7 +3864,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="720273" y="0"/>
+          <a:off x="3229430" y="0"/>
           <a:ext cx="1945808" cy="2552700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4252,7 +4401,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B0E35B-6A7A-48D2-B1DB-8AF96A63466D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91D3DF2A-3CFD-4A00-81D0-DD2999A7D89B}">
   <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
@@ -4276,7 +4425,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>601</v>
+        <v>649</v>
       </c>
       <c r="D4" t="s">
         <v>510</v>
@@ -4284,7 +4433,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>603</v>
+        <v>648</v>
       </c>
       <c r="D6" t="s">
         <v>511</v>
@@ -4292,7 +4441,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>602</v>
+        <v>650</v>
       </c>
       <c r="D8" t="s">
         <v>519</v>
@@ -4349,12 +4498,12 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="SWmLjaif2zNHS62CoMVZ9eVol1IoSdxNr6t1MPb2U8s0irsrCkz8ESCvo34fG56GDQXdYcSRSxj15/lx5h1gvQ==" saltValue="awjqA6oCzZhiwpc6UXWDRQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="9NVJH3z52WM3LKqCEaw+1ISq5AUCwTfdMKGw63KBpycxYfpXszHON8YpTGb+tIspuZCzO9bDtEMb964BQiabbg==" saltValue="O8A2uVtGY1bWI72wd0kjaQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatCells="0" insertRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D17" r:id="rId1" xr:uid="{24C562C0-6387-4B63-98CE-3C9E3FAF2EE4}"/>
-    <hyperlink ref="A1" r:id="rId2" display="『哥哥科技』" xr:uid="{34360349-868F-442B-9309-5DDB2E2EA2C2}"/>
-    <hyperlink ref="A2" r:id="rId3" display="https://qun.qq.com/universal-share/share?ac=1&amp;authKey=%2FWJ%2F4NS6lNp1cyU2a1kUo%2F%2FEfq8vD6q7SXUux2UosjZ%2BialqZVNe%2Bk3w1YoOUR3b&amp;busi_data=eyJncm91cENvZGUiOiI2ODA0NjQzNjUiLCJ0b2tlbiI6IkI5ZHVYaHJnSGlZZEpzSkRhamdOZFZaNy9aZFJ1L1JwNGpZYWNJWTJJRThGYjBoVjN6RUxhUkcvV0h4eHBwV2siLCJ1aW4iOiIxNTIwMDg1MjQ5In0%3D&amp;data=iHLL1DGOGIhddoSRjGmI9D2bMbNLa4vwx5YfZQAzvPM0sAuYo67cPN4265_UAPSpbgqWLVl8vmWBZVREf_Qg-g&amp;svctype=4&amp;tempid=h5_group_info" xr:uid="{762486EC-3F1C-4561-BBFC-7A0E8CD46672}"/>
+    <hyperlink ref="D17" r:id="rId1" xr:uid="{303B1002-FDEF-4B04-B4A4-2DD0B6E933ED}"/>
+    <hyperlink ref="A1" r:id="rId2" display="『哥哥科技』" xr:uid="{D70B4210-11B5-498B-9BBD-C4B93E15D3DB}"/>
+    <hyperlink ref="A2" r:id="rId3" display="https://qun.qq.com/universal-share/share?ac=1&amp;authKey=%2FWJ%2F4NS6lNp1cyU2a1kUo%2F%2FEfq8vD6q7SXUux2UosjZ%2BialqZVNe%2Bk3w1YoOUR3b&amp;busi_data=eyJncm91cENvZGUiOiI2ODA0NjQzNjUiLCJ0b2tlbiI6IkI5ZHVYaHJnSGlZZEpzSkRhamdOZFZaNy9aZFJ1L1JwNGpZYWNJWTJJRThGYjBoVjN6RUxhUkcvV0h4eHBwV2siLCJ1aW4iOiIxNTIwMDg1MjQ5In0%3D&amp;data=iHLL1DGOGIhddoSRjGmI9D2bMbNLa4vwx5YfZQAzvPM0sAuYo67cPN4265_UAPSpbgqWLVl8vmWBZVREf_Qg-g&amp;svctype=4&amp;tempid=h5_group_info" xr:uid="{448F38BA-50ED-4BD6-8215-EC161AF3DCF1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId4"/>
@@ -4392,10 +4541,10 @@
         <v>219</v>
       </c>
       <c r="H1" s="3"/>
-      <c r="I1" s="93" t="s">
+      <c r="I1" s="94" t="s">
         <v>220</v>
       </c>
-      <c r="J1" s="93"/>
+      <c r="J1" s="94"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="22">
@@ -4407,18 +4556,18 @@
       <c r="C2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="95" t="s">
+      <c r="D2" s="96" t="s">
         <v>495</v>
       </c>
-      <c r="F2" s="96" t="s">
+      <c r="F2" s="97" t="s">
         <v>235</v>
       </c>
-      <c r="G2" s="96"/>
+      <c r="G2" s="97"/>
       <c r="H2" s="12"/>
-      <c r="I2" s="97" t="s">
+      <c r="I2" s="98" t="s">
         <v>546</v>
       </c>
-      <c r="J2" s="97"/>
+      <c r="J2" s="98"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="22">
@@ -4430,7 +4579,7 @@
       <c r="C3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="95"/>
+      <c r="D3" s="96"/>
       <c r="E3" s="1">
         <v>90</v>
       </c>
@@ -4443,10 +4592,10 @@
       <c r="H3" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="I3" s="98" t="s">
+      <c r="I3" s="99" t="s">
         <v>234</v>
       </c>
-      <c r="J3" s="98"/>
+      <c r="J3" s="99"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="22">
@@ -4458,7 +4607,7 @@
       <c r="C4" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="95"/>
+      <c r="D4" s="96"/>
       <c r="E4" s="1">
         <v>91</v>
       </c>
@@ -4471,10 +4620,10 @@
       <c r="H4" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="I4" s="99" t="s">
+      <c r="I4" s="100" t="s">
         <v>240</v>
       </c>
-      <c r="J4" s="99"/>
+      <c r="J4" s="100"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="12">
@@ -4517,7 +4666,7 @@
         <v>118</v>
       </c>
       <c r="H6" s="3"/>
-      <c r="I6" s="101" t="s">
+      <c r="I6" s="102" t="s">
         <v>538</v>
       </c>
     </row>
@@ -4544,7 +4693,7 @@
         <v>119</v>
       </c>
       <c r="H7" s="3"/>
-      <c r="I7" s="101"/>
+      <c r="I7" s="102"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="22">
@@ -4569,7 +4718,7 @@
         <v>120</v>
       </c>
       <c r="H8" s="3"/>
-      <c r="I8" s="101"/>
+      <c r="I8" s="102"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="23">
@@ -4594,7 +4743,7 @@
         <v>121</v>
       </c>
       <c r="H9" s="3"/>
-      <c r="I9" s="101"/>
+      <c r="I9" s="102"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="22">
@@ -4619,7 +4768,7 @@
         <v>122</v>
       </c>
       <c r="H10" s="3"/>
-      <c r="I10" s="101"/>
+      <c r="I10" s="102"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="22">
@@ -4644,6 +4793,9 @@
         <v>123</v>
       </c>
       <c r="H11" s="3"/>
+      <c r="J11" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="22">
@@ -4668,6 +4820,12 @@
         <v>124</v>
       </c>
       <c r="H12" s="3"/>
+      <c r="I12" s="91" t="s">
+        <v>602</v>
+      </c>
+      <c r="J12" t="s">
+        <v>604</v>
+      </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="22">
@@ -4692,6 +4850,12 @@
         <v>125</v>
       </c>
       <c r="H13" s="3"/>
+      <c r="I13" t="s">
+        <v>606</v>
+      </c>
+      <c r="J13" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="22">
@@ -4716,6 +4880,12 @@
         <v>126</v>
       </c>
       <c r="H14" s="3"/>
+      <c r="I14" t="s">
+        <v>609</v>
+      </c>
+      <c r="J14" s="37" t="s">
+        <v>607</v>
+      </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="23">
@@ -4737,6 +4907,12 @@
         <v>127</v>
       </c>
       <c r="H15" s="3"/>
+      <c r="I15" t="s">
+        <v>611</v>
+      </c>
+      <c r="J15" s="37" t="s">
+        <v>608</v>
+      </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="12">
@@ -4758,8 +4934,14 @@
         <v>128</v>
       </c>
       <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16" t="s">
+        <v>610</v>
+      </c>
+      <c r="J16" s="37" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="23">
         <v>16</v>
       </c>
@@ -4782,8 +4964,14 @@
         <v>129</v>
       </c>
       <c r="H17" s="3"/>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17" t="s">
+        <v>612</v>
+      </c>
+      <c r="J17" s="37" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="23">
         <v>17</v>
       </c>
@@ -4806,8 +4994,14 @@
         <v>131</v>
       </c>
       <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="I18" t="s">
+        <v>194</v>
+      </c>
+      <c r="J18" s="37" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="23">
         <v>18</v>
       </c>
@@ -4828,8 +5022,14 @@
         <v>68</v>
       </c>
       <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="I19" t="s">
+        <v>613</v>
+      </c>
+      <c r="J19" s="37" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -4852,8 +5052,14 @@
         <v>133</v>
       </c>
       <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="I20" t="s">
+        <v>614</v>
+      </c>
+      <c r="J20" s="37" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -4873,8 +5079,14 @@
         <v>134</v>
       </c>
       <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="I21" t="s">
+        <v>615</v>
+      </c>
+      <c r="J21" s="37" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="22">
         <v>21</v>
       </c>
@@ -4899,8 +5111,9 @@
       <c r="H22" t="s">
         <v>561</v>
       </c>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="J22" s="37"/>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="42">
         <v>22</v>
       </c>
@@ -4923,8 +5136,14 @@
         <v>137</v>
       </c>
       <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="I23" t="s">
+        <v>626</v>
+      </c>
+      <c r="J23" s="37" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="22">
         <v>23</v>
       </c>
@@ -4947,8 +5166,14 @@
         <v>139</v>
       </c>
       <c r="H24" s="3"/>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="I24" t="s">
+        <v>627</v>
+      </c>
+      <c r="J24" s="37" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="22">
         <v>24</v>
       </c>
@@ -4973,8 +5198,14 @@
       <c r="H25" s="3" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="I25" t="s">
+        <v>628</v>
+      </c>
+      <c r="J25" s="37" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="22">
         <v>25</v>
       </c>
@@ -4999,8 +5230,14 @@
       <c r="H26" s="3" t="s">
         <v>560</v>
       </c>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="I26" t="s">
+        <v>629</v>
+      </c>
+      <c r="J26" s="37" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="22">
         <v>26</v>
       </c>
@@ -5021,7 +5258,7 @@
       </c>
       <c r="H27" s="3"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:10">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -5042,7 +5279,7 @@
       </c>
       <c r="H28" s="3"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:10">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -5063,7 +5300,7 @@
       </c>
       <c r="H29" s="3"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:10">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -5084,7 +5321,7 @@
       </c>
       <c r="H30" s="3"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:10">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -5105,7 +5342,7 @@
       </c>
       <c r="H31" s="3"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:10">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -5283,7 +5520,7 @@
       <c r="G39" s="62" t="s">
         <v>155</v>
       </c>
-      <c r="H39" s="94" t="s">
+      <c r="H39" s="95" t="s">
         <v>464</v>
       </c>
     </row>
@@ -5309,7 +5546,7 @@
       <c r="G40" s="62" t="s">
         <v>156</v>
       </c>
-      <c r="H40" s="95"/>
+      <c r="H40" s="96"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
@@ -5466,7 +5703,7 @@
       <c r="G47" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="H47" s="100" t="s">
+      <c r="H47" s="101" t="s">
         <v>507</v>
       </c>
     </row>
@@ -5489,7 +5726,7 @@
       <c r="G48" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="H48" s="100"/>
+      <c r="H48" s="101"/>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="1">
@@ -5514,7 +5751,7 @@
         <v>598</v>
       </c>
       <c r="I49" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -6683,24 +6920,24 @@
       <c r="C100" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="E100" s="102" t="s">
+      <c r="E100" s="103" t="s">
         <v>531</v>
       </c>
-      <c r="F100" s="102"/>
-      <c r="G100" s="102"/>
-      <c r="H100" s="102"/>
-      <c r="I100" s="102"/>
+      <c r="F100" s="103"/>
+      <c r="G100" s="103"/>
+      <c r="H100" s="103"/>
+      <c r="I100" s="103"/>
     </row>
     <row r="102" spans="1:9">
-      <c r="A102" s="95" t="s">
+      <c r="A102" s="96" t="s">
         <v>329</v>
       </c>
-      <c r="B102" s="95"/>
-      <c r="C102" s="95"/>
-      <c r="D102" s="95"/>
-      <c r="E102" s="95"/>
-      <c r="F102" s="95"/>
-      <c r="G102" s="95"/>
+      <c r="B102" s="96"/>
+      <c r="C102" s="96"/>
+      <c r="D102" s="96"/>
+      <c r="E102" s="96"/>
+      <c r="F102" s="96"/>
+      <c r="G102" s="96"/>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="1">
@@ -7429,7 +7666,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{004E8C14-01FA-4F79-B5F4-D85F586C9EEB}">
-  <dimension ref="A1:A145"/>
+  <dimension ref="A1:A164"/>
   <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
     <col min="1" max="1" width="21.0703125" customWidth="1"/>
@@ -7521,7 +7758,7 @@
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="103" t="s">
+      <c r="A19" s="93" t="s">
         <v>600</v>
       </c>
     </row>
@@ -8153,6 +8390,96 @@
     <row r="145" spans="1:1">
       <c r="A145" t="s">
         <v>462</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" t="s">
+        <v>647</v>
       </c>
     </row>
   </sheetData>
@@ -8172,25 +8499,25 @@
     <SignatureMethod Algorithm="http://www.w3.org/2001/04/xmldsig-more#rsa-sha256"/>
     <Reference Type="http://www.w3.org/2000/09/xmldsig#Object" URI="#idPackageObject">
       <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-      <DigestValue>/iySCV1sAc4ChOJjXW99beIeOVh8HbhHWSza7s91BQs=</DigestValue>
+      <DigestValue>B+bliFJsVk8wQTb9mv7Tn1vjeqdacbNSQfMl5o3NYLM=</DigestValue>
     </Reference>
     <Reference Type="http://www.w3.org/2000/09/xmldsig#Object" URI="#idOfficeObject">
       <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-      <DigestValue>XcuY37diGVrY5098uPDIo98BZLboXKR3lsb/SKaejlI=</DigestValue>
+      <DigestValue>Q6znH/hjrhR3EFDQFB0LioXqaUrrQoq0weDFY8ZNYVQ=</DigestValue>
     </Reference>
     <Reference Type="http://uri.etsi.org/01903#SignedProperties" URI="#idSignedProperties">
       <Transforms>
         <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
       </Transforms>
       <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-      <DigestValue>9KJs+r140Cxcn3wwLkEo96vs2yO1YEDRZDFRT3DAzHk=</DigestValue>
+      <DigestValue>X5zFNnu2moAniRJPeIfmP/uydxuaEgyQkAaM3xDxYVo=</DigestValue>
     </Reference>
   </SignedInfo>
-  <SignatureValue>H6n3/EYkzhvvsS1WNzkxwPZOy89EyZIECA8s8fNuaGU2AMOS0n4ceS8HMi2yHJkTpqQiQ9Z6w+U7
-Eq64LpTI1CZFuWFIQroGJkNHQ+7LfgeFfAia/FHDGXd40Zbf/8FpFvTh3Xa9ItlXZhZub4Te1+1e
-jXHzMQmIfnl1JnHcLI2XTDFU7Km0PT3y05RG9GmHzIPhesavu3om1IxMaRCIWoWgXS3fgqJpq+yn
-KYQZfbqzy5Q5sJ0FwHl4XKK4N8nonneAnCeMqVYem5a24SoFl7El/iIUeyfGA0rdBM2KhDWRy1Gy
-05TjPnTQZ45BI6h5pEtm2BhPMFlkzuwl1YAxOA==</SignatureValue>
+  <SignatureValue>ia17ZxhMYIFWSmw3FPzt7jiBTSriD1iilUVJ7m/yMkNsyls4aV4SuT9O5ZcsciD4T0oGL1nrwusu
+v3fl715EjyxH73Y7+uzV6woF+OO9dQf/TnLrV4MtgxgiU+O64hyHk8KaJuJqPIJrqb6F6hbNsLXj
+40bvs/+x3f14lokYmVLOR2epx6Fvl7uTG37/D9ero48yr0z5Nz8wUtYRgH8osv/sXmEQmsG5uGYe
+PHQvyFLpu9YXw4O4Mfopmtiq0waljV4hDe43n37fozremrCXZzROtjdqm6HSNszc4p58e0LvrfOM
+RDxCS+Razr9pF4yfwhltuSDZFu6rb6GGTB0hSA==</SignatureValue>
   <KeyInfo>
     <X509Data>
       <X509Certificate>MIIDujCCAqKgAwIBAgIK3DAIbS5AItImsDANBgkqhkiG9w0BAQsFADCBijEiMCAGA1UEAwwZ5LqR5aSp5piO5a6H5a6Z57O757ufVUNYTjEbMBkGA1UEChMSQU1EIFJ5emVuIDkgNzk0MEhYMRcwFQYDVQQLDA5RUee+pDY4MDQ2NDM2NTEhMB8GCSqGSIb3DQEJARYSNTAxNDMwMDQxQGJpbGliaWxpMQswCQYDVQQGEwJDTjAeFw0yNDA4MTIwMzExNDdaFw0yOTA4MTIwMzExNDdaMIGKMSIwIAYDVQQDDBnkupHlpKnmmI7lroflrpnns7vnu59VQ1hOMRswGQYDVQQKExJBTUQgUnl6ZW4gOSA3OTQwSFgxFzAVBgNVBAsMDlFR576kNjgwNDY0MzY1MSEwHwYJKoZIhvcNAQkBFhI1MDE0MzAwNDFAYmlsaWJpbGkxCzAJBgNVBAYTAkNOMIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA3hfxo46kNdl/MdVB15fJk0bD09CGechP9Xma8mSzh228fHNc/kXpCXDrcX4br/0b7gsOwZqI+YigaoBKJjMbFpT1dfMr7PRCmdWyGhcTJ18ROTczbYvGhYbz3pLcIcIk3tHNLzxjOfpmxTW5FaysUAdxpHrZ4SmhQtytFJD9A3qVSH860pNU1kRc3wK2M3nc0n5YAWUKzAX/upg8xhzXqjFvQrAJvyDwTcr+/y9TMM8A8qZbG6STBM2fpRZb5fIW+6xBdVVfwQ7odJLjZ4X2Mlqv1P3T3GazSZRHZHAtGrpPjVGYNs/5AE9jW7Vmc/4XhODQIYS4ULl9+yPMcyBbLwIDAQABoyAwHjAPBgkqhkiG9y8BAQoEAgUAMAsGA1UdDwQEAwIDmDANBgkqhkiG9w0BAQsFAAOCAQEAOCVHM+GIGHW7JvfyOrYBwPbTfubNFF9vWqxnOR1Eu1mAnPYcRiDkGwPEkX3kDq32CjR1wBanvHXzjJgkoY8TzxwAJZRnOE+MUjOQhlJ7RV7IG11QL52DKPvOZrYsUAG5gpOZ1VKxC3OewBwQ1TROcl9uVY0nOBrpNgyzkNZwE3JcKdKkBL1n3DQxQC1zHuNZ/AxYyH+GNNg90kP4xMEr/JunlWH/5cEM2rIwqI2o8pErx5dns56Ri/J9P2BzXUJ87h0nFePfEr/r/afCeMh5zYP6iZOkZdTSR4WSPBQsp0DmwbbeViyFQ0qkchqDsFktbDJ6s6SzfG0R3u6ZmAaE9g==</X509Certificate>
@@ -8211,16 +8538,16 @@
       <Reference URI="/xl/_rels/workbook.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
         <Transforms>
           <Transform Algorithm="http://schemas.openxmlformats.org/package/2006/RelationshipTransform">
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId2"/>
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId6"/>
-            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId5"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId10"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId4"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId9"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId8"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId3"/>
             <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId7"/>
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId2"/>
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId1"/>
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId6"/>
+            <mdssi:RelationshipReference xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature" SourceId="rId5"/>
           </Transform>
           <Transform Algorithm="http://www.w3.org/TR/2001/REC-xml-c14n-20010315"/>
         </Transforms>
@@ -8277,7 +8604,7 @@
       </Reference>
       <Reference URI="/xl/drawings/drawing2.xml?ContentType=application/vnd.openxmlformats-officedocument.drawing+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>CmVW1B3cFZYXjMhUshxzjEpc3Kix93TWDDFYyYV2+TE=</DigestValue>
+        <DigestValue>bLOZ9FFa1hfE3ukOLNWVajKohFwPz0BrZnK2/LDL77g=</DigestValue>
       </Reference>
       <Reference URI="/xl/drawings/drawing3.xml?ContentType=application/vnd.openxmlformats-officedocument.drawing+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
@@ -8317,11 +8644,11 @@
       </Reference>
       <Reference URI="/xl/sharedStrings.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.sharedStrings+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>+s4aGZPX7y6/LqxkyVSQti7Seg8HTbWjcwoDvnK2n2Y=</DigestValue>
+        <DigestValue>SMtqhDR7zjeVBImOpqVlsJvlXXhgbKcsTSlhrPx5qjQ=</DigestValue>
       </Reference>
       <Reference URI="/xl/styles.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.styles+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>h322m0N7JHW5I/4dGmf2WWcg0Tj/KgjpfyWhgXenEhA=</DigestValue>
+        <DigestValue>plCbGgE1uStnJFVVHeHMTyjZBRj5rOmw4uVlhnCqi8w=</DigestValue>
       </Reference>
       <Reference URI="/xl/theme/theme1.xml?ContentType=application/vnd.openxmlformats-officedocument.theme+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
@@ -8329,7 +8656,7 @@
       </Reference>
       <Reference URI="/xl/workbook.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.sheet.main+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>+JOphbxOQsdi+Jmx+TSWC4139qHV8Oxxj1Gg2fOPrmk=</DigestValue>
+        <DigestValue>8nZn65xtfH/U9c5hwg0zWUKGnaogivro4rZDQjZl0JM=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/_rels/sheet1.xml.rels?ContentType=application/vnd.openxmlformats-package.relationships+xml">
         <Transforms>
@@ -8401,11 +8728,11 @@
       </Reference>
       <Reference URI="/xl/worksheets/sheet2.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>/xb8IQ9Rg54Q5y6CSAJQEMM7MzJ1T2HidLzeP3LVuX4=</DigestValue>
+        <DigestValue>h+hrTVqPVWNFvVTtNxAaQGNWVl9H9jTZ6OvcW2GeZGs=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/sheet3.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>fPmWd7OC3EnlnSJ7vFpXkJw3pFnLQ3BtThMm8cEDlzI=</DigestValue>
+        <DigestValue>mz6pjG8ZAPIVTVfWT1SydllyPkF7mJWpsilS91QxIVo=</DigestValue>
       </Reference>
       <Reference URI="/xl/worksheets/sheet4.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
@@ -8421,14 +8748,14 @@
       </Reference>
       <Reference URI="/xl/worksheets/sheet7.xml?ContentType=application/vnd.openxmlformats-officedocument.spreadsheetml.worksheet+xml">
         <DigestMethod Algorithm="http://www.w3.org/2001/04/xmlenc#sha256"/>
-        <DigestValue>2MqJDcIeA7ml1JzKyC14LVs7PY41E3DrnjtS78DPyiY=</DigestValue>
+        <DigestValue>zIrAzJsJ2x+MYVMtGKcJmadRr+du2Z/vJd3OuRL/8DU=</DigestValue>
       </Reference>
     </Manifest>
     <SignatureProperties>
       <SignatureProperty Id="idSignatureTime" Target="#idPackageSignature">
         <mdssi:SignatureTime xmlns:mdssi="http://schemas.openxmlformats.org/package/2006/digital-signature">
           <mdssi:Format>YYYY-MM-DDThh:mm:ssTZD</mdssi:Format>
-          <mdssi:Value>2026-05-30T05:22:18Z</mdssi:Value>
+          <mdssi:Value>2026-09-16T15:12:55Z</mdssi:Value>
         </mdssi:SignatureTime>
       </SignatureProperty>
     </SignatureProperties>
@@ -8442,8 +8769,8 @@
           <SignatureImage/>
           <SignatureComments/>
           <WindowsVersion>10.0</WindowsVersion>
-          <OfficeVersion>16.0.20126/27</OfficeVersion>
-          <ApplicationVersion>16.0.20126</ApplicationVersion>
+          <OfficeVersion>16.0.20514/27</OfficeVersion>
+          <ApplicationVersion>16.0.20514</ApplicationVersion>
           <Monitors>1</Monitors>
           <HorizontalResolution>2560</HorizontalResolution>
           <VerticalResolution>1600</VerticalResolution>
@@ -8460,7 +8787,7 @@
     <xd:QualifyingProperties xmlns:xd="http://uri.etsi.org/01903/v1.3.2#" Target="#idPackageSignature">
       <xd:SignedProperties Id="idSignedProperties">
         <xd:SignedSignatureProperties>
-          <xd:SigningTime>2026-05-30T05:22:18Z</xd:SigningTime>
+          <xd:SigningTime>2026-09-16T15:12:55Z</xd:SigningTime>
           <xd:SigningCertificate>
             <xd:Cert>
               <xd:CertDigest>
